--- a/yamroute2_template.xlsx
+++ b/yamroute2_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Misha\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA969AF6-651C-41CD-871E-9580619C43B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9616D7B-0E6B-4EBB-A1A8-A5625DFC103F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4845" yWindow="810" windowWidth="29145" windowHeight="17700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Orders" sheetId="1" r:id="rId1"/>
@@ -487,6 +487,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -700,7 +703,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -764,20 +767,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -1203,58 +1210,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="36" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="38" t="s">
+      <c r="I1" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="37"/>
-      <c r="K1" s="34" t="s">
+      <c r="J1" s="35"/>
+      <c r="K1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="34" t="s">
+      <c r="L1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="34" t="s">
+      <c r="M1" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="34" t="s">
+      <c r="N1" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="34" t="s">
+      <c r="O1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="34" t="s">
+      <c r="P1" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="35" t="s">
+      <c r="Q1" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="37"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="35"/>
       <c r="U1" s="31" t="s">
         <v>15</v>
       </c>
@@ -29331,6 +29338,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="U1:U2"/>
     <mergeCell ref="X1:X2"/>
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="W1:W2"/>
@@ -29341,16 +29358,6 @@
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="U1:U2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" location="order-id" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -29508,10 +29515,10 @@
       <c r="B3" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="39" t="s">
         <v>82</v>
       </c>
       <c r="E3" s="27" t="s">
@@ -29557,10 +29564,10 @@
       <c r="B4" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="40" t="s">
         <v>84</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -29606,10 +29613,10 @@
       <c r="B5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="40" t="s">
         <v>86</v>
       </c>
       <c r="E5" s="8" t="s">

--- a/yamroute2_template.xlsx
+++ b/yamroute2_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Misha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Misha\Desktop\СБС\Резюме\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9616D7B-0E6B-4EBB-A1A8-A5625DFC103F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481C25B3-09AF-4229-B470-463B98C43CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4845" yWindow="810" windowWidth="29145" windowHeight="17700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Orders" sheetId="1" r:id="rId1"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="82">
   <si>
     <t>Идентификатор заказа</t>
   </si>
@@ -449,24 +449,6 @@
   </si>
   <si>
     <t>ДНС ТЕХНОПОИНТ</t>
-  </si>
-  <si>
-    <t>60.099120</t>
-  </si>
-  <si>
-    <t>30.260082</t>
-  </si>
-  <si>
-    <t>59.779367</t>
-  </si>
-  <si>
-    <t>30.171706</t>
-  </si>
-  <si>
-    <t>59.932468</t>
-  </si>
-  <si>
-    <t>30.351810</t>
   </si>
   <si>
     <r>
@@ -763,28 +745,28 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -1210,50 +1192,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="36" t="s">
-        <v>87</v>
+      <c r="G1" s="33" t="s">
+        <v>81</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="35"/>
-      <c r="K1" s="33" t="s">
+      <c r="J1" s="39"/>
+      <c r="K1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="33" t="s">
+      <c r="P1" s="35" t="s">
         <v>13</v>
       </c>
       <c r="Q1" s="37" t="s">
@@ -1261,43 +1243,43 @@
       </c>
       <c r="R1" s="38"/>
       <c r="S1" s="38"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="31" t="s">
+      <c r="T1" s="39"/>
+      <c r="U1" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="31" t="s">
+      <c r="V1" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="W1" s="31" t="s">
+      <c r="W1" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="X1" s="31" t="s">
+      <c r="X1" s="36" t="s">
         <v>69</v>
       </c>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
       <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
       <c r="Q2" s="3" t="s">
         <v>20</v>
       </c>
@@ -1310,10 +1292,10 @@
       <c r="T2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="34"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
@@ -29338,16 +29320,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="U1:U2"/>
     <mergeCell ref="X1:X2"/>
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="W1:W2"/>
@@ -29358,6 +29330,16 @@
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="U1:U2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" location="order-id" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -29515,12 +29497,8 @@
       <c r="B3" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="39" t="s">
-        <v>82</v>
-      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
       <c r="E3" s="27" t="s">
         <v>75</v>
       </c>
@@ -29564,12 +29542,8 @@
       <c r="B4" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="40" t="s">
-        <v>84</v>
-      </c>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
       <c r="E4" s="8" t="s">
         <v>76</v>
       </c>
@@ -29613,12 +29587,8 @@
       <c r="B5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" s="40" t="s">
-        <v>86</v>
-      </c>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="8" t="s">
         <v>77</v>
       </c>
